--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62836-2025 artfynd.xlsx
+++ b/artfynd/A 62836-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137253956</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137253959</v>
       </c>
       <c r="B3" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137253955</v>
       </c>
       <c r="B4" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137250905</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>137253957</v>
       </c>
       <c r="B6" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
